--- a/config/aggregations/exiobase/units.xlsx
+++ b/config/aggregations/exiobase/units.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer_website\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\research\exiobase-explorer\exiobase_explorer\config\aggregations\exiobase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D312800C-6B55-4B31-BC50-D656BE334F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A63BA06-3195-4ED3-BB5A-C81538466677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="exiobase" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2884" uniqueCount="365">
   <si>
     <t>impact_key</t>
   </si>
@@ -1089,6 +1089,36 @@
   </si>
   <si>
     <t>kilómetros cuadrados</t>
+  </si>
+  <si>
+    <t>Tsd. Km²</t>
+  </si>
+  <si>
+    <t>Mio. km²</t>
+  </si>
+  <si>
+    <t>Mrd. km²</t>
+  </si>
+  <si>
+    <t>Tausdend km²</t>
+  </si>
+  <si>
+    <t>Millionen km²</t>
+  </si>
+  <si>
+    <t>Milliarden km²</t>
+  </si>
+  <si>
+    <t>Gh</t>
+  </si>
+  <si>
+    <t>Milliarden Stunden</t>
+  </si>
+  <si>
+    <t>Th</t>
+  </si>
+  <si>
+    <t>Billionen Stunden</t>
   </si>
 </sst>
 </file>
@@ -1429,9 +1459,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I127"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1460,7 +1490,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1489,7 +1519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1518,7 +1548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1547,7 +1577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1576,7 +1606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1605,7 +1635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1634,7 +1664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1663,7 +1693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1692,7 +1722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1721,7 +1751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1750,7 +1780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -1779,7 +1809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -1808,7 +1838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -1837,7 +1867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -1866,7 +1896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1895,7 +1925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -1924,7 +1954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -1953,7 +1983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1982,7 +2012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -2011,7 +2041,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -2040,7 +2070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -2069,7 +2099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -2098,7 +2128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -2127,7 +2157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -2156,7 +2186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -2185,7 +2215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -2214,7 +2244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -2243,7 +2273,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -2272,7 +2302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -2301,7 +2331,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>55</v>
       </c>
@@ -2330,7 +2360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>56</v>
       </c>
@@ -2359,7 +2389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>57</v>
       </c>
@@ -2388,7 +2418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -2417,7 +2447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>59</v>
       </c>
@@ -2446,7 +2476,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -2475,7 +2505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>61</v>
       </c>
@@ -2504,7 +2534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>62</v>
       </c>
@@ -2533,7 +2563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>63</v>
       </c>
@@ -2562,7 +2592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>65</v>
       </c>
@@ -2591,7 +2621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>66</v>
       </c>
@@ -2620,7 +2650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>67</v>
       </c>
@@ -2649,7 +2679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>70</v>
       </c>
@@ -2678,7 +2708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>71</v>
       </c>
@@ -2707,7 +2737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>72</v>
       </c>
@@ -2736,7 +2766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>73</v>
       </c>
@@ -2765,7 +2795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>74</v>
       </c>
@@ -2794,7 +2824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>75</v>
       </c>
@@ -2823,7 +2853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>76</v>
       </c>
@@ -2852,7 +2882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -2881,7 +2911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>78</v>
       </c>
@@ -2910,7 +2940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>79</v>
       </c>
@@ -2939,7 +2969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -2968,7 +2998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -2997,7 +3027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>84</v>
       </c>
@@ -3026,7 +3056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>85</v>
       </c>
@@ -3055,7 +3085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>86</v>
       </c>
@@ -3084,7 +3114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>87</v>
       </c>
@@ -3113,7 +3143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>88</v>
       </c>
@@ -3142,7 +3172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>89</v>
       </c>
@@ -3171,7 +3201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>90</v>
       </c>
@@ -3200,7 +3230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>91</v>
       </c>
@@ -3229,7 +3259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>92</v>
       </c>
@@ -3258,7 +3288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>93</v>
       </c>
@@ -3287,7 +3317,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -3316,7 +3346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>95</v>
       </c>
@@ -3345,7 +3375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>96</v>
       </c>
@@ -3374,7 +3404,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>97</v>
       </c>
@@ -3403,7 +3433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>98</v>
       </c>
@@ -3432,7 +3462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>99</v>
       </c>
@@ -3461,7 +3491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>100</v>
       </c>
@@ -3490,7 +3520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>101</v>
       </c>
@@ -3519,7 +3549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>102</v>
       </c>
@@ -3548,7 +3578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>103</v>
       </c>
@@ -3577,7 +3607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>104</v>
       </c>
@@ -3606,7 +3636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>105</v>
       </c>
@@ -3635,7 +3665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>106</v>
       </c>
@@ -3664,7 +3694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>108</v>
       </c>
@@ -3693,7 +3723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>109</v>
       </c>
@@ -3722,7 +3752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>111</v>
       </c>
@@ -3751,7 +3781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>112</v>
       </c>
@@ -3780,7 +3810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>113</v>
       </c>
@@ -3809,7 +3839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>115</v>
       </c>
@@ -3838,7 +3868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>116</v>
       </c>
@@ -3867,7 +3897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>118</v>
       </c>
@@ -3896,7 +3926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>120</v>
       </c>
@@ -3925,7 +3955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>121</v>
       </c>
@@ -3954,7 +3984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>123</v>
       </c>
@@ -3983,7 +4013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>124</v>
       </c>
@@ -4012,7 +4042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>126</v>
       </c>
@@ -4041,7 +4071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>128</v>
       </c>
@@ -4070,7 +4100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>130</v>
       </c>
@@ -4099,7 +4129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>131</v>
       </c>
@@ -4128,7 +4158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>132</v>
       </c>
@@ -4157,7 +4187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>134</v>
       </c>
@@ -4186,7 +4216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>135</v>
       </c>
@@ -4215,7 +4245,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>137</v>
       </c>
@@ -4244,7 +4274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>138</v>
       </c>
@@ -4273,7 +4303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>140</v>
       </c>
@@ -4302,7 +4332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -4331,7 +4361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>142</v>
       </c>
@@ -4360,7 +4390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>144</v>
       </c>
@@ -4389,7 +4419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>146</v>
       </c>
@@ -4418,7 +4448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>148</v>
       </c>
@@ -4447,7 +4477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>149</v>
       </c>
@@ -4476,7 +4506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>150</v>
       </c>
@@ -4505,7 +4535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>151</v>
       </c>
@@ -4534,7 +4564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>152</v>
       </c>
@@ -4563,7 +4593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -4592,7 +4622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>154</v>
       </c>
@@ -4621,7 +4651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>155</v>
       </c>
@@ -4650,7 +4680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>156</v>
       </c>
@@ -4679,7 +4709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>157</v>
       </c>
@@ -4708,7 +4738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>158</v>
       </c>
@@ -4737,7 +4767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>159</v>
       </c>
@@ -4766,7 +4796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>160</v>
       </c>
@@ -4795,7 +4825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>161</v>
       </c>
@@ -4824,7 +4854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>162</v>
       </c>
@@ -4853,7 +4883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>163</v>
       </c>
@@ -4882,7 +4912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>164</v>
       </c>
@@ -4911,7 +4941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>165</v>
       </c>
@@ -4940,7 +4970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>166</v>
       </c>
@@ -4969,7 +4999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>167</v>
       </c>
@@ -4998,7 +5028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>168</v>
       </c>
@@ -5027,7 +5057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>169</v>
       </c>
@@ -5056,7 +5086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>170</v>
       </c>
@@ -5085,7 +5115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>171</v>
       </c>
@@ -5122,15 +5152,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U134"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.33203125" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>173</v>
       </c>
@@ -5195,7 +5231,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>194</v>
       </c>
@@ -5206,7 +5242,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>197</v>
       </c>
@@ -5217,7 +5253,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>197</v>
       </c>
@@ -5228,7 +5264,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>197</v>
       </c>
@@ -5239,7 +5275,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>197</v>
       </c>
@@ -5256,7 +5292,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>197</v>
       </c>
@@ -5270,7 +5306,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>197</v>
       </c>
@@ -5284,7 +5320,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>197</v>
       </c>
@@ -5298,7 +5334,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>197</v>
       </c>
@@ -5312,7 +5348,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>197</v>
       </c>
@@ -5326,7 +5362,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>197</v>
       </c>
@@ -5340,7 +5376,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>197</v>
       </c>
@@ -5354,7 +5390,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>197</v>
       </c>
@@ -5368,7 +5404,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>197</v>
       </c>
@@ -5382,7 +5418,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>197</v>
       </c>
@@ -5396,7 +5432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>197</v>
       </c>
@@ -5410,7 +5446,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>197</v>
       </c>
@@ -5424,7 +5460,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>197</v>
       </c>
@@ -5438,7 +5474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>197</v>
       </c>
@@ -5452,7 +5488,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>197</v>
       </c>
@@ -5466,7 +5502,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>197</v>
       </c>
@@ -5480,7 +5516,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>197</v>
       </c>
@@ -5494,7 +5530,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>197</v>
       </c>
@@ -5508,7 +5544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>197</v>
       </c>
@@ -5522,7 +5558,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>197</v>
       </c>
@@ -5536,7 +5572,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>197</v>
       </c>
@@ -5550,7 +5586,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>197</v>
       </c>
@@ -5561,7 +5597,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>197</v>
       </c>
@@ -5572,7 +5608,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>197</v>
       </c>
@@ -5583,7 +5619,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>197</v>
       </c>
@@ -5594,7 +5630,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>197</v>
       </c>
@@ -5605,7 +5641,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>197</v>
       </c>
@@ -5616,7 +5652,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>197</v>
       </c>
@@ -5627,7 +5663,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>197</v>
       </c>
@@ -5638,7 +5674,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>197</v>
       </c>
@@ -5649,7 +5685,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>197</v>
       </c>
@@ -5660,7 +5696,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>197</v>
       </c>
@@ -5671,7 +5707,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>197</v>
       </c>
@@ -5682,7 +5718,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>197</v>
       </c>
@@ -5693,7 +5729,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>197</v>
       </c>
@@ -5704,7 +5740,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>197</v>
       </c>
@@ -5715,7 +5751,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>197</v>
       </c>
@@ -5732,7 +5768,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>197</v>
       </c>
@@ -5749,7 +5785,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>197</v>
       </c>
@@ -5766,7 +5802,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>197</v>
       </c>
@@ -5777,7 +5813,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>197</v>
       </c>
@@ -5788,7 +5824,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>197</v>
       </c>
@@ -5805,7 +5841,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>197</v>
       </c>
@@ -5822,7 +5858,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>197</v>
       </c>
@@ -5839,7 +5875,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>197</v>
       </c>
@@ -5856,7 +5892,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>197</v>
       </c>
@@ -5873,7 +5909,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>197</v>
       </c>
@@ -5890,7 +5926,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>197</v>
       </c>
@@ -5907,7 +5943,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>197</v>
       </c>
@@ -5924,7 +5960,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>197</v>
       </c>
@@ -5941,7 +5977,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>197</v>
       </c>
@@ -5958,7 +5994,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>197</v>
       </c>
@@ -5975,7 +6011,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>197</v>
       </c>
@@ -5992,7 +6028,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>197</v>
       </c>
@@ -6009,7 +6045,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>197</v>
       </c>
@@ -6026,7 +6062,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>197</v>
       </c>
@@ -6043,7 +6079,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>197</v>
       </c>
@@ -6060,7 +6096,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>197</v>
       </c>
@@ -6077,7 +6113,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>197</v>
       </c>
@@ -6094,7 +6130,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>197</v>
       </c>
@@ -6111,7 +6147,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>197</v>
       </c>
@@ -6128,7 +6164,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>197</v>
       </c>
@@ -6145,7 +6181,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>197</v>
       </c>
@@ -6162,7 +6198,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>197</v>
       </c>
@@ -6179,7 +6215,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>197</v>
       </c>
@@ -6196,7 +6232,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>197</v>
       </c>
@@ -6213,7 +6249,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>197</v>
       </c>
@@ -6230,7 +6266,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -6247,7 +6283,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>197</v>
       </c>
@@ -6264,7 +6300,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>197</v>
       </c>
@@ -6281,7 +6317,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>197</v>
       </c>
@@ -6298,7 +6334,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>197</v>
       </c>
@@ -6315,7 +6351,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>197</v>
       </c>
@@ -6332,7 +6368,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>197</v>
       </c>
@@ -6349,7 +6385,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>197</v>
       </c>
@@ -6366,7 +6402,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>197</v>
       </c>
@@ -6383,7 +6419,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>197</v>
       </c>
@@ -6400,7 +6436,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>197</v>
       </c>
@@ -6417,7 +6453,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>197</v>
       </c>
@@ -6434,7 +6470,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>197</v>
       </c>
@@ -6451,7 +6487,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>197</v>
       </c>
@@ -6462,7 +6498,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>197</v>
       </c>
@@ -6479,7 +6515,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>197</v>
       </c>
@@ -6493,7 +6529,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>197</v>
       </c>
@@ -6507,7 +6543,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>197</v>
       </c>
@@ -6521,7 +6557,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>197</v>
       </c>
@@ -6535,7 +6571,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>197</v>
       </c>
@@ -6549,7 +6585,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>197</v>
       </c>
@@ -6563,7 +6599,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>197</v>
       </c>
@@ -6580,7 +6616,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>197</v>
       </c>
@@ -6594,7 +6630,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>197</v>
       </c>
@@ -6611,7 +6647,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>197</v>
       </c>
@@ -6625,7 +6661,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>197</v>
       </c>
@@ -6639,7 +6675,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>197</v>
       </c>
@@ -6653,7 +6689,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>197</v>
       </c>
@@ -6667,7 +6703,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>197</v>
       </c>
@@ -6684,7 +6720,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>197</v>
       </c>
@@ -6698,7 +6734,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>197</v>
       </c>
@@ -6712,7 +6748,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>197</v>
       </c>
@@ -6729,7 +6765,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>197</v>
       </c>
@@ -6740,7 +6776,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>197</v>
       </c>
@@ -6751,7 +6787,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>197</v>
       </c>
@@ -6762,7 +6798,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>197</v>
       </c>
@@ -6773,7 +6809,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>197</v>
       </c>
@@ -6784,7 +6820,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>197</v>
       </c>
@@ -6795,7 +6831,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>197</v>
       </c>
@@ -6806,7 +6842,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>197</v>
       </c>
@@ -6817,7 +6853,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>197</v>
       </c>
@@ -6828,7 +6864,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>197</v>
       </c>
@@ -6839,7 +6875,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>197</v>
       </c>
@@ -6850,7 +6886,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>197</v>
       </c>
@@ -6861,7 +6897,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>197</v>
       </c>
@@ -6872,7 +6908,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>197</v>
       </c>
@@ -6883,7 +6919,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>197</v>
       </c>
@@ -6894,7 +6930,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>197</v>
       </c>
@@ -6905,7 +6941,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>197</v>
       </c>
@@ -6916,7 +6952,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>197</v>
       </c>
@@ -6927,7 +6963,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>197</v>
       </c>
@@ -6938,7 +6974,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>197</v>
       </c>
@@ -6949,7 +6985,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>197</v>
       </c>
@@ -6960,7 +6996,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>197</v>
       </c>
@@ -6971,7 +7007,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>197</v>
       </c>
@@ -6982,7 +7018,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>217</v>
       </c>
@@ -7026,7 +7062,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>217</v>
       </c>
@@ -7058,7 +7094,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>217</v>
       </c>
@@ -7083,8 +7119,20 @@
       <c r="Q131" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="R131" t="s">
+        <v>361</v>
+      </c>
+      <c r="S131" t="s">
+        <v>362</v>
+      </c>
+      <c r="T131" t="s">
+        <v>363</v>
+      </c>
+      <c r="U131" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>217</v>
       </c>
@@ -7116,7 +7164,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>217</v>
       </c>
@@ -7154,7 +7202,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>217</v>
       </c>
@@ -7172,6 +7220,24 @@
       </c>
       <c r="M134" t="s">
         <v>263</v>
+      </c>
+      <c r="N134" t="s">
+        <v>355</v>
+      </c>
+      <c r="O134" t="s">
+        <v>358</v>
+      </c>
+      <c r="P134" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>359</v>
+      </c>
+      <c r="R134" t="s">
+        <v>357</v>
+      </c>
+      <c r="S134" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -7182,9 +7248,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U134"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>173</v>
       </c>
@@ -7249,7 +7315,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>194</v>
       </c>
@@ -7260,7 +7326,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>197</v>
       </c>
@@ -7271,7 +7337,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>197</v>
       </c>
@@ -7282,7 +7348,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>197</v>
       </c>
@@ -7293,7 +7359,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>197</v>
       </c>
@@ -7310,7 +7376,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>197</v>
       </c>
@@ -7324,7 +7390,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>197</v>
       </c>
@@ -7338,7 +7404,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>197</v>
       </c>
@@ -7352,7 +7418,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>197</v>
       </c>
@@ -7366,7 +7432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>197</v>
       </c>
@@ -7380,7 +7446,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>197</v>
       </c>
@@ -7394,7 +7460,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>197</v>
       </c>
@@ -7408,7 +7474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>197</v>
       </c>
@@ -7422,7 +7488,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>197</v>
       </c>
@@ -7436,7 +7502,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>197</v>
       </c>
@@ -7450,7 +7516,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>197</v>
       </c>
@@ -7464,7 +7530,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>197</v>
       </c>
@@ -7478,7 +7544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>197</v>
       </c>
@@ -7492,7 +7558,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>197</v>
       </c>
@@ -7506,7 +7572,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>197</v>
       </c>
@@ -7520,7 +7586,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>197</v>
       </c>
@@ -7534,7 +7600,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>197</v>
       </c>
@@ -7548,7 +7614,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>197</v>
       </c>
@@ -7562,7 +7628,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>197</v>
       </c>
@@ -7576,7 +7642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>197</v>
       </c>
@@ -7590,7 +7656,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>197</v>
       </c>
@@ -7604,7 +7670,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>197</v>
       </c>
@@ -7615,7 +7681,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>197</v>
       </c>
@@ -7626,7 +7692,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>197</v>
       </c>
@@ -7637,7 +7703,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>197</v>
       </c>
@@ -7648,7 +7714,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>197</v>
       </c>
@@ -7659,7 +7725,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>197</v>
       </c>
@@ -7670,7 +7736,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>197</v>
       </c>
@@ -7681,7 +7747,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>197</v>
       </c>
@@ -7692,7 +7758,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>197</v>
       </c>
@@ -7703,7 +7769,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>197</v>
       </c>
@@ -7714,7 +7780,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>197</v>
       </c>
@@ -7725,7 +7791,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>197</v>
       </c>
@@ -7736,7 +7802,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>197</v>
       </c>
@@ -7747,7 +7813,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>197</v>
       </c>
@@ -7758,7 +7824,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>197</v>
       </c>
@@ -7769,7 +7835,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>197</v>
       </c>
@@ -7786,7 +7852,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>197</v>
       </c>
@@ -7803,7 +7869,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>197</v>
       </c>
@@ -7820,7 +7886,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>197</v>
       </c>
@@ -7831,7 +7897,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>197</v>
       </c>
@@ -7842,7 +7908,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>197</v>
       </c>
@@ -7859,7 +7925,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>197</v>
       </c>
@@ -7876,7 +7942,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>197</v>
       </c>
@@ -7893,7 +7959,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>197</v>
       </c>
@@ -7910,7 +7976,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>197</v>
       </c>
@@ -7927,7 +7993,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>197</v>
       </c>
@@ -7944,7 +8010,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>197</v>
       </c>
@@ -7961,7 +8027,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>197</v>
       </c>
@@ -7978,7 +8044,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>197</v>
       </c>
@@ -7995,7 +8061,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>197</v>
       </c>
@@ -8012,7 +8078,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>197</v>
       </c>
@@ -8029,7 +8095,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>197</v>
       </c>
@@ -8046,7 +8112,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>197</v>
       </c>
@@ -8063,7 +8129,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>197</v>
       </c>
@@ -8080,7 +8146,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>197</v>
       </c>
@@ -8097,7 +8163,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>197</v>
       </c>
@@ -8114,7 +8180,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>197</v>
       </c>
@@ -8131,7 +8197,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>197</v>
       </c>
@@ -8148,7 +8214,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>197</v>
       </c>
@@ -8165,7 +8231,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>197</v>
       </c>
@@ -8182,7 +8248,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>197</v>
       </c>
@@ -8199,7 +8265,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>197</v>
       </c>
@@ -8216,7 +8282,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>197</v>
       </c>
@@ -8233,7 +8299,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>197</v>
       </c>
@@ -8250,7 +8316,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>197</v>
       </c>
@@ -8267,7 +8333,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>197</v>
       </c>
@@ -8284,7 +8350,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -8301,7 +8367,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>197</v>
       </c>
@@ -8318,7 +8384,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>197</v>
       </c>
@@ -8335,7 +8401,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>197</v>
       </c>
@@ -8352,7 +8418,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>197</v>
       </c>
@@ -8369,7 +8435,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>197</v>
       </c>
@@ -8386,7 +8452,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>197</v>
       </c>
@@ -8403,7 +8469,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>197</v>
       </c>
@@ -8420,7 +8486,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>197</v>
       </c>
@@ -8437,7 +8503,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>197</v>
       </c>
@@ -8454,7 +8520,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>197</v>
       </c>
@@ -8471,7 +8537,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>197</v>
       </c>
@@ -8488,7 +8554,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>197</v>
       </c>
@@ -8505,7 +8571,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>197</v>
       </c>
@@ -8516,7 +8582,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>197</v>
       </c>
@@ -8533,7 +8599,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>197</v>
       </c>
@@ -8547,7 +8613,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>197</v>
       </c>
@@ -8561,7 +8627,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>197</v>
       </c>
@@ -8575,7 +8641,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>197</v>
       </c>
@@ -8589,7 +8655,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>197</v>
       </c>
@@ -8603,7 +8669,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>197</v>
       </c>
@@ -8617,7 +8683,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>197</v>
       </c>
@@ -8634,7 +8700,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>197</v>
       </c>
@@ -8648,7 +8714,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>197</v>
       </c>
@@ -8665,7 +8731,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>197</v>
       </c>
@@ -8679,7 +8745,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>197</v>
       </c>
@@ -8693,7 +8759,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>197</v>
       </c>
@@ -8707,7 +8773,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>197</v>
       </c>
@@ -8721,7 +8787,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>197</v>
       </c>
@@ -8738,7 +8804,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>197</v>
       </c>
@@ -8752,7 +8818,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>197</v>
       </c>
@@ -8766,7 +8832,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>197</v>
       </c>
@@ -8783,7 +8849,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>197</v>
       </c>
@@ -8794,7 +8860,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>197</v>
       </c>
@@ -8805,7 +8871,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>197</v>
       </c>
@@ -8816,7 +8882,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>197</v>
       </c>
@@ -8827,7 +8893,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>197</v>
       </c>
@@ -8838,7 +8904,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>197</v>
       </c>
@@ -8849,7 +8915,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>197</v>
       </c>
@@ -8860,7 +8926,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>197</v>
       </c>
@@ -8871,7 +8937,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>197</v>
       </c>
@@ -8882,7 +8948,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>197</v>
       </c>
@@ -8893,7 +8959,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>197</v>
       </c>
@@ -8904,7 +8970,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>197</v>
       </c>
@@ -8915,7 +8981,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>197</v>
       </c>
@@ -8926,7 +8992,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>197</v>
       </c>
@@ -8937,7 +9003,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>197</v>
       </c>
@@ -8948,7 +9014,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>197</v>
       </c>
@@ -8959,7 +9025,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>197</v>
       </c>
@@ -8970,7 +9036,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>197</v>
       </c>
@@ -8981,7 +9047,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>197</v>
       </c>
@@ -8992,7 +9058,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>197</v>
       </c>
@@ -9003,7 +9069,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>197</v>
       </c>
@@ -9014,7 +9080,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>197</v>
       </c>
@@ -9025,7 +9091,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>197</v>
       </c>
@@ -9036,7 +9102,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>217</v>
       </c>
@@ -9074,7 +9140,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>217</v>
       </c>
@@ -9106,7 +9172,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>217</v>
       </c>
@@ -9132,7 +9198,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>217</v>
       </c>
@@ -9164,7 +9230,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>217</v>
       </c>
@@ -9202,7 +9268,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>217</v>
       </c>
@@ -9230,9 +9296,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:U134"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>173</v>
       </c>
@@ -9297,7 +9363,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>194</v>
       </c>
@@ -9305,7 +9371,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>197</v>
       </c>
@@ -9316,7 +9382,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>197</v>
       </c>
@@ -9327,7 +9393,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>197</v>
       </c>
@@ -9338,7 +9404,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>197</v>
       </c>
@@ -9355,7 +9421,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>197</v>
       </c>
@@ -9369,7 +9435,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>197</v>
       </c>
@@ -9383,7 +9449,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>197</v>
       </c>
@@ -9397,7 +9463,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>197</v>
       </c>
@@ -9411,7 +9477,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>197</v>
       </c>
@@ -9425,7 +9491,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>197</v>
       </c>
@@ -9439,7 +9505,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>197</v>
       </c>
@@ -9453,7 +9519,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>197</v>
       </c>
@@ -9467,7 +9533,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>197</v>
       </c>
@@ -9481,7 +9547,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>197</v>
       </c>
@@ -9495,7 +9561,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>197</v>
       </c>
@@ -9509,7 +9575,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>197</v>
       </c>
@@ -9523,7 +9589,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>197</v>
       </c>
@@ -9537,7 +9603,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>197</v>
       </c>
@@ -9551,7 +9617,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>197</v>
       </c>
@@ -9565,7 +9631,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>197</v>
       </c>
@@ -9579,7 +9645,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>197</v>
       </c>
@@ -9593,7 +9659,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>197</v>
       </c>
@@ -9607,7 +9673,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>197</v>
       </c>
@@ -9621,7 +9687,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>197</v>
       </c>
@@ -9635,7 +9701,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>197</v>
       </c>
@@ -9649,7 +9715,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>197</v>
       </c>
@@ -9660,7 +9726,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>197</v>
       </c>
@@ -9671,7 +9737,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>197</v>
       </c>
@@ -9682,7 +9748,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>197</v>
       </c>
@@ -9693,7 +9759,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>197</v>
       </c>
@@ -9704,7 +9770,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>197</v>
       </c>
@@ -9715,7 +9781,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>197</v>
       </c>
@@ -9726,7 +9792,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>197</v>
       </c>
@@ -9737,7 +9803,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>197</v>
       </c>
@@ -9748,7 +9814,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>197</v>
       </c>
@@ -9759,7 +9825,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>197</v>
       </c>
@@ -9770,7 +9836,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>197</v>
       </c>
@@ -9781,7 +9847,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>197</v>
       </c>
@@ -9792,7 +9858,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>197</v>
       </c>
@@ -9803,7 +9869,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>197</v>
       </c>
@@ -9814,7 +9880,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>197</v>
       </c>
@@ -9831,7 +9897,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>197</v>
       </c>
@@ -9848,7 +9914,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>197</v>
       </c>
@@ -9865,7 +9931,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>197</v>
       </c>
@@ -9876,7 +9942,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>197</v>
       </c>
@@ -9887,7 +9953,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>197</v>
       </c>
@@ -9904,7 +9970,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>197</v>
       </c>
@@ -9921,7 +9987,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>197</v>
       </c>
@@ -9938,7 +10004,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>197</v>
       </c>
@@ -9955,7 +10021,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>197</v>
       </c>
@@ -9972,7 +10038,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>197</v>
       </c>
@@ -9989,7 +10055,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>197</v>
       </c>
@@ -10006,7 +10072,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>197</v>
       </c>
@@ -10023,7 +10089,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>197</v>
       </c>
@@ -10040,7 +10106,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>197</v>
       </c>
@@ -10057,7 +10123,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>197</v>
       </c>
@@ -10074,7 +10140,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>197</v>
       </c>
@@ -10091,7 +10157,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>197</v>
       </c>
@@ -10108,7 +10174,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>197</v>
       </c>
@@ -10125,7 +10191,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>197</v>
       </c>
@@ -10142,7 +10208,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>197</v>
       </c>
@@ -10159,7 +10225,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>197</v>
       </c>
@@ -10176,7 +10242,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>197</v>
       </c>
@@ -10193,7 +10259,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>197</v>
       </c>
@@ -10210,7 +10276,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>197</v>
       </c>
@@ -10227,7 +10293,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>197</v>
       </c>
@@ -10244,7 +10310,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>197</v>
       </c>
@@ -10261,7 +10327,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>197</v>
       </c>
@@ -10278,7 +10344,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>197</v>
       </c>
@@ -10295,7 +10361,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>197</v>
       </c>
@@ -10312,7 +10378,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>197</v>
       </c>
@@ -10329,7 +10395,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -10346,7 +10412,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>197</v>
       </c>
@@ -10363,7 +10429,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>197</v>
       </c>
@@ -10380,7 +10446,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>197</v>
       </c>
@@ -10397,7 +10463,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>197</v>
       </c>
@@ -10414,7 +10480,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>197</v>
       </c>
@@ -10431,7 +10497,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>197</v>
       </c>
@@ -10448,7 +10514,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>197</v>
       </c>
@@ -10465,7 +10531,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>197</v>
       </c>
@@ -10482,7 +10548,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>197</v>
       </c>
@@ -10499,7 +10565,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>197</v>
       </c>
@@ -10516,7 +10582,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>197</v>
       </c>
@@ -10533,7 +10599,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>197</v>
       </c>
@@ -10550,7 +10616,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>197</v>
       </c>
@@ -10561,7 +10627,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>197</v>
       </c>
@@ -10578,7 +10644,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>197</v>
       </c>
@@ -10592,7 +10658,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>197</v>
       </c>
@@ -10606,7 +10672,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>197</v>
       </c>
@@ -10620,7 +10686,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>197</v>
       </c>
@@ -10634,7 +10700,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>197</v>
       </c>
@@ -10648,7 +10714,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>197</v>
       </c>
@@ -10662,7 +10728,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>197</v>
       </c>
@@ -10679,7 +10745,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>197</v>
       </c>
@@ -10693,7 +10759,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>197</v>
       </c>
@@ -10710,7 +10776,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>197</v>
       </c>
@@ -10724,7 +10790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>197</v>
       </c>
@@ -10738,7 +10804,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>197</v>
       </c>
@@ -10752,7 +10818,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>197</v>
       </c>
@@ -10766,7 +10832,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>197</v>
       </c>
@@ -10783,7 +10849,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>197</v>
       </c>
@@ -10797,7 +10863,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>197</v>
       </c>
@@ -10811,7 +10877,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>197</v>
       </c>
@@ -10828,7 +10894,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>197</v>
       </c>
@@ -10839,7 +10905,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>197</v>
       </c>
@@ -10850,7 +10916,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>197</v>
       </c>
@@ -10861,7 +10927,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>197</v>
       </c>
@@ -10872,7 +10938,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>197</v>
       </c>
@@ -10883,7 +10949,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>197</v>
       </c>
@@ -10894,7 +10960,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>197</v>
       </c>
@@ -10905,7 +10971,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>197</v>
       </c>
@@ -10916,7 +10982,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>197</v>
       </c>
@@ -10927,7 +10993,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>197</v>
       </c>
@@ -10938,7 +11004,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>197</v>
       </c>
@@ -10949,7 +11015,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>197</v>
       </c>
@@ -10960,7 +11026,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>197</v>
       </c>
@@ -10971,7 +11037,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>197</v>
       </c>
@@ -10982,7 +11048,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>197</v>
       </c>
@@ -10993,7 +11059,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>197</v>
       </c>
@@ -11004,7 +11070,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>197</v>
       </c>
@@ -11015,7 +11081,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>197</v>
       </c>
@@ -11026,7 +11092,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>197</v>
       </c>
@@ -11037,7 +11103,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>197</v>
       </c>
@@ -11048,7 +11114,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>197</v>
       </c>
@@ -11059,7 +11125,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>197</v>
       </c>
@@ -11070,7 +11136,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>197</v>
       </c>
@@ -11081,7 +11147,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>217</v>
       </c>
@@ -11119,7 +11185,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>217</v>
       </c>
@@ -11151,7 +11217,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>217</v>
       </c>
@@ -11177,7 +11243,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>217</v>
       </c>
@@ -11209,7 +11275,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>217</v>
       </c>
@@ -11247,7 +11313,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>217</v>
       </c>
@@ -11275,9 +11341,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:U134"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>173</v>
       </c>
@@ -11342,7 +11408,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>194</v>
       </c>
@@ -11353,7 +11419,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>197</v>
       </c>
@@ -11364,7 +11430,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>197</v>
       </c>
@@ -11375,7 +11441,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>197</v>
       </c>
@@ -11386,7 +11452,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>197</v>
       </c>
@@ -11403,7 +11469,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>197</v>
       </c>
@@ -11417,7 +11483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>197</v>
       </c>
@@ -11431,7 +11497,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>197</v>
       </c>
@@ -11445,7 +11511,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>197</v>
       </c>
@@ -11459,7 +11525,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>197</v>
       </c>
@@ -11473,7 +11539,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>197</v>
       </c>
@@ -11487,7 +11553,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>197</v>
       </c>
@@ -11501,7 +11567,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>197</v>
       </c>
@@ -11515,7 +11581,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>197</v>
       </c>
@@ -11529,7 +11595,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>197</v>
       </c>
@@ -11543,7 +11609,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>197</v>
       </c>
@@ -11557,7 +11623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>197</v>
       </c>
@@ -11571,7 +11637,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>197</v>
       </c>
@@ -11585,7 +11651,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>197</v>
       </c>
@@ -11599,7 +11665,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>197</v>
       </c>
@@ -11613,7 +11679,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>197</v>
       </c>
@@ -11627,7 +11693,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>197</v>
       </c>
@@ -11641,7 +11707,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>197</v>
       </c>
@@ -11655,7 +11721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>197</v>
       </c>
@@ -11669,7 +11735,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>197</v>
       </c>
@@ -11683,7 +11749,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>197</v>
       </c>
@@ -11697,7 +11763,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>197</v>
       </c>
@@ -11708,7 +11774,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>197</v>
       </c>
@@ -11719,7 +11785,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>197</v>
       </c>
@@ -11730,7 +11796,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>197</v>
       </c>
@@ -11741,7 +11807,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>197</v>
       </c>
@@ -11752,7 +11818,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>197</v>
       </c>
@@ -11763,7 +11829,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>197</v>
       </c>
@@ -11774,7 +11840,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>197</v>
       </c>
@@ -11785,7 +11851,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>197</v>
       </c>
@@ -11796,7 +11862,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>197</v>
       </c>
@@ -11807,7 +11873,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>197</v>
       </c>
@@ -11818,7 +11884,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>197</v>
       </c>
@@ -11829,7 +11895,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>197</v>
       </c>
@@ -11840,7 +11906,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>197</v>
       </c>
@@ -11851,7 +11917,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>197</v>
       </c>
@@ -11862,7 +11928,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>197</v>
       </c>
@@ -11879,7 +11945,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>197</v>
       </c>
@@ -11896,7 +11962,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>197</v>
       </c>
@@ -11913,7 +11979,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>197</v>
       </c>
@@ -11924,7 +11990,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>197</v>
       </c>
@@ -11935,7 +12001,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>197</v>
       </c>
@@ -11952,7 +12018,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>197</v>
       </c>
@@ -11969,7 +12035,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>197</v>
       </c>
@@ -11986,7 +12052,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>197</v>
       </c>
@@ -12003,7 +12069,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>197</v>
       </c>
@@ -12020,7 +12086,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>197</v>
       </c>
@@ -12037,7 +12103,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>197</v>
       </c>
@@ -12054,7 +12120,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>197</v>
       </c>
@@ -12071,7 +12137,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>197</v>
       </c>
@@ -12088,7 +12154,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>197</v>
       </c>
@@ -12105,7 +12171,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>197</v>
       </c>
@@ -12122,7 +12188,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>197</v>
       </c>
@@ -12139,7 +12205,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>197</v>
       </c>
@@ -12156,7 +12222,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>197</v>
       </c>
@@ -12173,7 +12239,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>197</v>
       </c>
@@ -12190,7 +12256,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>197</v>
       </c>
@@ -12207,7 +12273,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>197</v>
       </c>
@@ -12224,7 +12290,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>197</v>
       </c>
@@ -12241,7 +12307,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>197</v>
       </c>
@@ -12258,7 +12324,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>197</v>
       </c>
@@ -12275,7 +12341,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>197</v>
       </c>
@@ -12292,7 +12358,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>197</v>
       </c>
@@ -12309,7 +12375,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>197</v>
       </c>
@@ -12326,7 +12392,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>197</v>
       </c>
@@ -12343,7 +12409,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>197</v>
       </c>
@@ -12360,7 +12426,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>197</v>
       </c>
@@ -12377,7 +12443,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -12394,7 +12460,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>197</v>
       </c>
@@ -12411,7 +12477,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>197</v>
       </c>
@@ -12428,7 +12494,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>197</v>
       </c>
@@ -12445,7 +12511,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>197</v>
       </c>
@@ -12462,7 +12528,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>197</v>
       </c>
@@ -12479,7 +12545,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>197</v>
       </c>
@@ -12496,7 +12562,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>197</v>
       </c>
@@ -12513,7 +12579,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>197</v>
       </c>
@@ -12530,7 +12596,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>197</v>
       </c>
@@ -12547,7 +12613,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>197</v>
       </c>
@@ -12564,7 +12630,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>197</v>
       </c>
@@ -12581,7 +12647,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>197</v>
       </c>
@@ -12598,7 +12664,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>197</v>
       </c>
@@ -12609,7 +12675,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>197</v>
       </c>
@@ -12626,7 +12692,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>197</v>
       </c>
@@ -12640,7 +12706,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>197</v>
       </c>
@@ -12654,7 +12720,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>197</v>
       </c>
@@ -12668,7 +12734,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>197</v>
       </c>
@@ -12682,7 +12748,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>197</v>
       </c>
@@ -12696,7 +12762,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>197</v>
       </c>
@@ -12710,7 +12776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>197</v>
       </c>
@@ -12727,7 +12793,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>197</v>
       </c>
@@ -12741,7 +12807,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>197</v>
       </c>
@@ -12758,7 +12824,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>197</v>
       </c>
@@ -12772,7 +12838,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>197</v>
       </c>
@@ -12786,7 +12852,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>197</v>
       </c>
@@ -12800,7 +12866,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>197</v>
       </c>
@@ -12814,7 +12880,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>197</v>
       </c>
@@ -12831,7 +12897,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>197</v>
       </c>
@@ -12845,7 +12911,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>197</v>
       </c>
@@ -12859,7 +12925,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>197</v>
       </c>
@@ -12876,7 +12942,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>197</v>
       </c>
@@ -12887,7 +12953,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>197</v>
       </c>
@@ -12898,7 +12964,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>197</v>
       </c>
@@ -12909,7 +12975,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>197</v>
       </c>
@@ -12920,7 +12986,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>197</v>
       </c>
@@ -12931,7 +12997,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>197</v>
       </c>
@@ -12942,7 +13008,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>197</v>
       </c>
@@ -12953,7 +13019,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>197</v>
       </c>
@@ -12964,7 +13030,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>197</v>
       </c>
@@ -12975,7 +13041,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>197</v>
       </c>
@@ -12986,7 +13052,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>197</v>
       </c>
@@ -12997,7 +13063,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>197</v>
       </c>
@@ -13008,7 +13074,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>197</v>
       </c>
@@ -13019,7 +13085,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>197</v>
       </c>
@@ -13030,7 +13096,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>197</v>
       </c>
@@ -13041,7 +13107,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>197</v>
       </c>
@@ -13052,7 +13118,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>197</v>
       </c>
@@ -13063,7 +13129,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>197</v>
       </c>
@@ -13074,7 +13140,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>197</v>
       </c>
@@ -13085,7 +13151,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>197</v>
       </c>
@@ -13096,7 +13162,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>197</v>
       </c>
@@ -13107,7 +13173,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>197</v>
       </c>
@@ -13118,7 +13184,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>197</v>
       </c>
@@ -13129,7 +13195,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>217</v>
       </c>
@@ -13167,7 +13233,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>217</v>
       </c>
@@ -13199,7 +13265,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>217</v>
       </c>
@@ -13225,7 +13291,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>217</v>
       </c>
@@ -13257,7 +13323,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>217</v>
       </c>
@@ -13295,7 +13361,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>217</v>
       </c>
